--- a/jpcore-r4/develop-kohetest/observations-summary.xlsx
+++ b/jpcore-r4/develop-kohetest/observations-summary.xlsx
@@ -59,7 +59,7 @@
     <t/>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationBodyMeasurementCode_VS (preferred)</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationBodyMeasurementCode_VS|1.1.0 (preferred)</t>
   </si>
   <si>
     <t>dateTime, Period</t>
@@ -83,7 +83,7 @@
     <t>null#57133-1</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1 (example)</t>
   </si>
   <si>
     <t>dateTime</t>
@@ -146,7 +146,7 @@
     <t>JP Core Simple Observation Category CodeSystem#procedure, LOINC#LP7796-8</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationEndoscopyCode_VS (preferred)</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationEndoscopyCode_VS|1.3.0-dev (preferred)</t>
   </si>
   <si>
     <t>dateTimeĵ, Periodĵ</t>
@@ -164,7 +164,7 @@
     <t>JP Core Simple Observation Category CodeSystem#laboratory</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationLabResultCode_VS (preferred)</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationLabResultCode_VS|1.1.0 (preferred)</t>
   </si>
   <si>
     <t>dateTime, Period, Timing</t>
@@ -182,7 +182,7 @@
     <t>JP Core Simple Observation Category CodeSystem#laboratory, LOINC#18725-2</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationLabResultCode_VS (required)</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationLabResultCode_VS|1.1.0 (required)</t>
   </si>
   <si>
     <t>jp-observation-physicalexam</t>
@@ -197,7 +197,7 @@
     <t>null#physical-findings</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_PhysicalExamCode_VS (required)</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_PhysicalExamCode_VS|1.1.0 (required)</t>
   </si>
   <si>
     <t>jp-observation-radiology-findings</t>
@@ -233,7 +233,7 @@
     <t>JP Core Simple Observation Category CodeSystem#social-history</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationSocialHistoryCode_VS (preferred)</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationSocialHistoryCode_VS|1.1.0 (preferred)</t>
   </si>
   <si>
     <t>jp-observation-vitalsigns</t>
@@ -245,7 +245,7 @@
     <t>JP Core Simple Observation Category CodeSystem#vital-signs</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationVitalSignsCode_VS (preferred)</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationVitalSignsCode_VS|1.1.0 (preferred)</t>
   </si>
 </sst>
 </file>

--- a/jpcore-r4/develop-kohetest/observations-summary.xlsx
+++ b/jpcore-r4/develop-kohetest/observations-summary.xlsx
@@ -59,7 +59,7 @@
     <t/>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationBodyMeasurementCode_VS|1.1.0 (preferred)</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationBodyMeasurementCode_VS (preferred)</t>
   </si>
   <si>
     <t>dateTime, Period</t>
@@ -83,7 +83,7 @@
     <t>null#57133-1</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1 (example)</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes (example)</t>
   </si>
   <si>
     <t>dateTime</t>
@@ -146,7 +146,7 @@
     <t>JP Core Simple Observation Category CodeSystem#procedure, LOINC#LP7796-8</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationEndoscopyCode_VS|1.3.0-dev (preferred)</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationEndoscopyCode_VS (preferred)</t>
   </si>
   <si>
     <t>dateTimeĵ, Periodĵ</t>
@@ -164,7 +164,7 @@
     <t>JP Core Simple Observation Category CodeSystem#laboratory</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationLabResultCode_VS|1.1.0 (preferred)</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationLabResultCode_VS (preferred)</t>
   </si>
   <si>
     <t>dateTime, Period, Timing</t>
@@ -182,7 +182,7 @@
     <t>JP Core Simple Observation Category CodeSystem#laboratory, LOINC#18725-2</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationLabResultCode_VS|1.1.0 (required)</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationLabResultCode_VS (required)</t>
   </si>
   <si>
     <t>jp-observation-physicalexam</t>
@@ -197,7 +197,7 @@
     <t>null#physical-findings</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_PhysicalExamCode_VS|1.1.0 (required)</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_PhysicalExamCode_VS (required)</t>
   </si>
   <si>
     <t>jp-observation-radiology-findings</t>
@@ -233,7 +233,7 @@
     <t>JP Core Simple Observation Category CodeSystem#social-history</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationSocialHistoryCode_VS|1.1.0 (preferred)</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationSocialHistoryCode_VS (preferred)</t>
   </si>
   <si>
     <t>jp-observation-vitalsigns</t>
@@ -245,7 +245,7 @@
     <t>JP Core Simple Observation Category CodeSystem#vital-signs</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationVitalSignsCode_VS|1.1.0 (preferred)</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_ObservationVitalSignsCode_VS (preferred)</t>
   </si>
 </sst>
 </file>
